--- a/2022 data/excel_outputs/20_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/20_boothwise_data.xlsx
@@ -14,933 +14,1005 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="351">
   <si>
     <t>AC 20 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0##### ####. 3</t>
-  </si>
-  <si>
-    <t>####0##0#########</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ######</t>
-  </si>
-  <si>
-    <t>######### ######## ####. 1</t>
-  </si>
-  <si>
-    <t>######### ######## ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ####. 2</t>
-  </si>
-  <si>
-    <t>###### ## ####### ####. 1</t>
-  </si>
-  <si>
-    <t>###### ## ####### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####. 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ##0 ###### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##0 ###### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0###### ####### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0###### ####### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### ####. 3</t>
-  </si>
-  <si>
-    <t>####0##0##### ###### #### #### ####### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ###### #### #### ####### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##0### ####</t>
-  </si>
-  <si>
-    <t>####0##0######### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0######### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0######### ##### ####. 3</t>
-  </si>
-  <si>
-    <t>######## ######### ##### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>######## ######### ##### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>###### ## ##0### ####</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>####0##0####### ###</t>
-  </si>
-  <si>
-    <t>####0##0###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ##0### #######</t>
-  </si>
-  <si>
-    <t>####0##0####### ###### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0####### ###### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0##### ####</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####.1</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0##### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0###### ######## ####.1</t>
-  </si>
-  <si>
-    <t>####0##0###### ######## ####.2</t>
-  </si>
-  <si>
-    <t>#0#####0##0##0 ###### ######## ####. 1</t>
-  </si>
-  <si>
-    <t>#0#####0##0##0 ###### ######## ####. 2</t>
-  </si>
-  <si>
-    <t>#0#####0##0##0 ###### ######## ####. 3</t>
-  </si>
-  <si>
-    <t>####0##0####### #####</t>
-  </si>
-  <si>
-    <t>####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0######### ######</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ###### #### ####.1</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ###### #### ####.2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ###### #### ####.3</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ###### #### ####.4</t>
-  </si>
-  <si>
-    <t>####### ####0##0 ######0###### ####.1</t>
-  </si>
-  <si>
-    <t>####### ####0##0 ######0###### ####.2</t>
-  </si>
-  <si>
-    <t>####### ####0##0 ######0###### ####.3</t>
-  </si>
-  <si>
-    <t>##0##0#0##0###### ####.1</t>
-  </si>
-  <si>
-    <t>##0##0#0##0###### ####.2</t>
-  </si>
-  <si>
-    <t>##0##0#0##0###### ####.3</t>
-  </si>
-  <si>
-    <t>##0##0#0##0###### ####.4</t>
-  </si>
-  <si>
-    <t>##0##0#0##0###### ####.5</t>
-  </si>
-  <si>
-    <t>##0##0#0##0###### ####.6</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ###### ####.3</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ###### ####.4</t>
-  </si>
-  <si>
-    <t>####### #####0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>####### #####0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>####### #####0##0 ###### ####.3</t>
-  </si>
-  <si>
-    <t>##### ##### ######## ######## ###### ####.5</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### ######</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ####.1</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ####.2</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ####.3</t>
-  </si>
-  <si>
-    <t>###### ####0 ##### ###### ####.1</t>
-  </si>
-  <si>
-    <t>###### ####0 ##### ###### ####.2</t>
-  </si>
-  <si>
-    <t>###### ####0 ##### ###### ####.3</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ######</t>
-  </si>
-  <si>
-    <t>##0#0##0##0##0##### ###### ####.1</t>
-  </si>
-  <si>
-    <t>##0#0##0##0##0##### ###### ####.2</t>
-  </si>
-  <si>
-    <t>#0#0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>#0#0##0 ###### ####. 2</t>
-  </si>
-  <si>
-    <t>#0#0##0 ###### ####.3</t>
-  </si>
-  <si>
-    <t>### ##### ###### ####.5</t>
-  </si>
-  <si>
-    <t>### #0##0###### ####.1</t>
-  </si>
-  <si>
-    <t>### #0##0###### ####.2</t>
-  </si>
-  <si>
-    <t>### #0##0 ###### ####.3</t>
-  </si>
-  <si>
-    <t>### #0##0 ###### ####.4</t>
-  </si>
-  <si>
-    <t>##### #0##0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>##### #0##0##0 ###### ####. 2</t>
-  </si>
-  <si>
-    <t>##### #0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>##### #0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>##0##0########### ##### ######</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ######## ###### ####.3</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ######## ###### ####.4</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ####.2</t>
-  </si>
-  <si>
-    <t>#### ### ###### #0#0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>#### ### ###### #0#0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>#### ### ###### #0#0##0 ###### ####.3</t>
-  </si>
-  <si>
-    <t>#### ### ###### #0#0##0 ###### ####.4</t>
-  </si>
-  <si>
-    <t>#### ### ###### #0#0##0 ###### ####.5</t>
-  </si>
-  <si>
-    <t>#### ### ###### #0#0##0 ###### ####.6</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.1</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.3</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.4</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.5</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.6</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.7</t>
-  </si>
-  <si>
-    <t>##0##0##0#0 ##### ###### ####.8</t>
-  </si>
-  <si>
-    <t>####0##0####### ##### ###### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0####### ##### ###### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ###### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ###### ####. 2</t>
-  </si>
-  <si>
-    <t>####0######## ###### ####. 1</t>
-  </si>
-  <si>
-    <t>####0######## ###### ####. 2</t>
-  </si>
-  <si>
-    <t>#### ##0#0##0###### ####. 1</t>
-  </si>
-  <si>
-    <t>#### ##0#0##0###### ####. 2</t>
-  </si>
-  <si>
-    <t>#### ##0#0##0###### ####. 3</t>
-  </si>
-  <si>
-    <t>#### ##0#0##0###### ####. 4</t>
-  </si>
-  <si>
-    <t>#### ##0#0##0###### ####. 5</t>
-  </si>
-  <si>
-    <t>#### ##0#0##0###### ####. 6</t>
-  </si>
-  <si>
-    <t>##0#0#0#0##0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>##0#0#0#0##0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.1</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.3</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.4</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.5</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.6</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.7</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.8</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.9</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0###### ####.10</t>
-  </si>
-  <si>
-    <t>######### ##### ###### #### ###### ####.1</t>
-  </si>
-  <si>
-    <t>######### ##### ###### #### ###### ####.2</t>
-  </si>
-  <si>
-    <t>######### ##### ###### #### ###### ####.3</t>
-  </si>
-  <si>
-    <t>######### ##### ###### #### ###### ####.4</t>
-  </si>
-  <si>
-    <t>######### ##### ###### #### ###### ####.5</t>
-  </si>
-  <si>
-    <t>##0##0##0####0##0###### ####.1</t>
-  </si>
-  <si>
-    <t>##0##0##0####0##0###### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #########</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### #### ########## ####.1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### #### ########## ####.2</t>
-  </si>
-  <si>
-    <t>####0##0####### ##### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0####### ##### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>#### #0##0######## ####.1</t>
-  </si>
-  <si>
-    <t>#### #0##0######## ####.2</t>
-  </si>
-  <si>
-    <t>#### #0##0######## ####.3</t>
-  </si>
-  <si>
-    <t>####0##0##### ###</t>
-  </si>
-  <si>
-    <t>####0##0########## ####.1</t>
-  </si>
-  <si>
-    <t>####0##0########## ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #######</t>
-  </si>
-  <si>
-    <t>######## #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ###### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ###### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0######## ####.1</t>
-  </si>
-  <si>
-    <t>####0##0######## ####.2</t>
-  </si>
-  <si>
-    <t>####0##0######## ####.3</t>
-  </si>
-  <si>
-    <t>##### ####### ########</t>
-  </si>
-  <si>
-    <t>###### ## ######## ####.1</t>
-  </si>
-  <si>
-    <t>###### ## ######## ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####### ####. 2</t>
-  </si>
-  <si>
-    <t>#####0##0##0 ##### ####.1</t>
-  </si>
-  <si>
-    <t>#####0##0##0 ##### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##### ####.2</t>
-  </si>
-  <si>
-    <t>##### ####### ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ####.3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ####.4</t>
-  </si>
-  <si>
-    <t>##### #0##0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>###### #0##0 ####### ##### ####.1</t>
-  </si>
-  <si>
-    <t>###### #0##0 ####### ##### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0##### ####### ####</t>
-  </si>
-  <si>
-    <t>#0##### ##0##0 ###### ####### ####. 1</t>
-  </si>
-  <si>
-    <t>#0##### ##0##0 ###### ####### ####. 2</t>
-  </si>
-  <si>
-    <t>#0##### ##0##0 ###### ####### ####. 3</t>
-  </si>
-  <si>
-    <t>####0##0############## ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0############## ####. 2</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0######## #### ####.1</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0######## #### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0##0### ####</t>
-  </si>
-  <si>
-    <t>####0##0##0###### ###### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0##0###### ###### ####.2</t>
-  </si>
-  <si>
-    <t>###### ## ######### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ##### ####. 3</t>
-  </si>
-  <si>
-    <t>####0##0####### ### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0####### ### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ##### ######## ####. ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ##### ######## ####. ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0###########</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ####.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####</t>
-  </si>
-  <si>
-    <t>##0#0##0#0##0####### ####.1</t>
-  </si>
-  <si>
-    <t>##0#0##0#0##0####### ####.2</t>
-  </si>
-  <si>
-    <t>##0#0##0#0##0####### ####.3</t>
-  </si>
-  <si>
-    <t>#### ####### ### ##### ##### ####### ####.4</t>
-  </si>
-  <si>
-    <t>#### ####### ### ##### ##### ####### ####.5</t>
-  </si>
-  <si>
-    <t>#### ####### ### ##### ##### ####### ####.6</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####. 3</t>
-  </si>
-  <si>
-    <t>#####0##0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0###### ##### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0##### #### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0##### #### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ######</t>
-  </si>
-  <si>
-    <t>####0##0######### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0######### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ####.2</t>
-  </si>
-  <si>
-    <t>#####0##0##0 ####### ####. 1</t>
-  </si>
-  <si>
-    <t>#####0##0##0 ####### ####. 2</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ####### ##0#### ;########ddh ####. 1</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ####### ##0#### ;########ddh ####. 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0#### ####. 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0#### ####. 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #####</t>
-  </si>
-  <si>
-    <t>### ## ##0 ####### ####.1</t>
-  </si>
-  <si>
-    <t>### ## ##0 ####### ####.2</t>
-  </si>
-  <si>
-    <t>### ## ##0 ####### ####.3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####.3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####.4</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####.5</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####.1</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####.2</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####.3</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####.4</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####.5</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####.6</t>
-  </si>
-  <si>
-    <t>##0####0#0##0 ######## ####. 7</t>
-  </si>
-  <si>
-    <t>##0##0##0###0##0 ########</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ####### ######## ####.1</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ####### ######## ####.2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.1</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.3</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.4</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.5</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.6</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.7</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.8</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.9</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.10</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.11</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## ####.12</t>
-  </si>
-  <si>
-    <t>##### #0##0######## ####.1</t>
-  </si>
-  <si>
-    <t>##### #0##0######## ####.2</t>
-  </si>
-  <si>
-    <t>##### #0##0######## ####.3</t>
-  </si>
-  <si>
-    <t>##### #0##0######## ####.4</t>
-  </si>
-  <si>
-    <t>####### ### ###### ##### #0##0######## ####.1</t>
-  </si>
-  <si>
-    <t>####### ### ###### ##### #0##0######## ####.2</t>
-  </si>
-  <si>
-    <t>####### ### ###### ##### #0##0######## ####.3</t>
-  </si>
-  <si>
-    <t>####### ### ###### ##### #0##0######## ####.4</t>
-  </si>
-  <si>
-    <t>####### ### ###### ##### #0##0######## ####.5</t>
-  </si>
-  <si>
-    <t>##0####0#####0#0##0######## ####.1</t>
-  </si>
-  <si>
-    <t>##0####0#####0#0##0######## ####.2</t>
-  </si>
-  <si>
-    <t>##0####0#####0#0##0######## ####.3</t>
-  </si>
-  <si>
-    <t>##0####0#####0#0##0######## ####.4</t>
-  </si>
-  <si>
-    <t>##0####0#####0#0##0######## ####.5</t>
-  </si>
-  <si>
-    <t>####0##0#### #######</t>
-  </si>
-  <si>
-    <t>####0##0###### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0###### ####.2</t>
-  </si>
-  <si>
-    <t>##0 ######## ######### ####### ###### ####</t>
-  </si>
-  <si>
-    <t>##### ##0##0##### ######## ####.1</t>
-  </si>
-  <si>
-    <t>##### ##0##0##### ######## ####.2</t>
+    <t>PRA0VI0 TIV.DI KAKSH N0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TIV.DI KAKSH N0 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TIV.DI KAKSH N0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BURAHANAGAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAKIMAPUR MEGHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0AURAMGASHAHAPUR BANAVARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HUSAINAPUR HAMID</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHURA.DA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KOPA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHALIPUR NICHAL KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHALIPUR NICHAL KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT GHAR NATHADORI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KODIPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NURAPUR CHIPARI KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NURAPUR CHIPARI KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BADASHAHAPUR LAKSHMISAIN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0ALIPUR LALAMAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AJAMAPUR JAMANIBHAN KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AJAMAPUR JAMANIBHAN KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SADATABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAVADA SAIDAPUR JALAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHATEHAPUR JAMAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR JAMAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0HAPHIJABAD SHARKI KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0HAPHIJABAD SHARKI KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0HAPHIJABAD SHARKI KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAIDARAPUR</t>
+  </si>
+  <si>
+    <t>KISANAJU0HA0SKUL MUBARAKAPUR TAPPA BHARATI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ASAPHABAD BHAVAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UMARAPUR BAMGAR</t>
+  </si>
+  <si>
+    <t>PAMCHAYATAGHAR MAU0PUR SADA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAJARAULA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHATEHAPUR LAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHEKHAPUR BHAB.DA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAKASHAHAJANI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR SULTAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAKIMAPUR SHAKARAGAMJ KAKSH NAM. 1</t>
+  </si>
+  <si>
+    <t>40 CHTAPAUMTAL AIBIVAVAS BHMAPAUMCHANATAM AIMAMTAMHAMURAM TVAVAU CHAVAN 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALI LADAN KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALI LADAN KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALI LADAN KAKSH-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA GANNA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA NAINASI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 RAMATHERA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 VAJIRAPUR BHAGAVAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHAMAPUR HUSAINAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHAMAPUR HUSAINAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>KANYA PU0MA0VI0 DHAMAPUR HUSAINAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RASULAPUR IMMA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALADINAPUR BHATAPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAJUPURA</t>
+  </si>
+  <si>
+    <t>AR0ES0EM0I0KA0 RAMAPUR BHOLA KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>AR0ES0EM0I0KA0 RAMAPUR BHOLA KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>AR0ES0EM0I0KA0 RAMAPUR BHOLA KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0ALIPUR INAYAT</t>
+  </si>
+  <si>
+    <t>SARASVATI PRA0VI0 N0KSHE0 DHAMAPUR KAKSH SAM0-1</t>
+  </si>
+  <si>
+    <t>SARASVATI PRA0VI0 N0KSHE0 DHAMAPUR KAKSH SAM0-2</t>
+  </si>
+  <si>
+    <t>KE0EM0I0 KA0 DHAMAPUR KAKSH SAM0-01</t>
+  </si>
+  <si>
+    <t>KE0EM0I0 KA0 DHAMAPUR KAKSH SAM0-02</t>
+  </si>
+  <si>
+    <t>KE0EM0I0 KA0 DHAMAPUR KAKSH SAM0-03</t>
+  </si>
+  <si>
+    <t>K0 PURV MA0 VIDYALAY DHAMAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>K0 PURV MA0 VIDYALAY DHAMAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 DHAMAPUR KAKSH-03</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 DHAMAPUR KAKSH-04</t>
+  </si>
+  <si>
+    <t>LAKSHMI K0PA0 DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>LAKSHMIK0PA0 DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>LAKSHMIK0PA0 DHAMAPUR KAKSH-03</t>
+  </si>
+  <si>
+    <t>LAKSHMI K0PA0 DHAMAPUR KAKSH-04</t>
+  </si>
+  <si>
+    <t>PRA0VI0TILAK SKUL DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>PRA0VI0TILAK SKUL DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>SHIAVAJI N0PA0 SKUL DHAMAPUR KAKSH-1</t>
+  </si>
+  <si>
+    <t>75EPAMAMRAP CHAVAN .CMEJ AIBIVAVAS KIMUMCHANATAM TVAVAU.0 2</t>
+  </si>
+  <si>
+    <t>GO0KRRI0GOKHALE SKUL DHAMAPUR</t>
+  </si>
+  <si>
+    <t>BA0U0MA0VI0SHIA0 PARK DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>BA0U0MA0VI0SHIA0 PARK DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>KE0 EM0 I0 KALEJ DHAMAPUR QAKSH NAM0 4</t>
+  </si>
+  <si>
+    <t>K0U0MA0VI0 DHAMAPUR</t>
+  </si>
+  <si>
+    <t>MADARASA I0PU0 DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>MADARASA I0PU0 DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>MADARASA I0PU0 DHAMAPUR KAKSH-03</t>
+  </si>
+  <si>
+    <t>JU0HA0ARABIYA MADARASA DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>JU0HA0ARABIYA MADARASA DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>JAIN K0PA0 DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>JAIN K0PA0 DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>JAIN K0PA0 DHAMAPUR KAKSH-03</t>
+  </si>
+  <si>
+    <t>K0I0KA0 DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>K0I0KA0 DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>K0I0KA0 DHAMAPUR KAKSH-03</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHOTA SHIAV MANIDAR DHAMAPUR KAKSH-01</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHOTA SHIAV MANIDAR DHAMAPUR KAKSH-02</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALAVALAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DITTANAPUR</t>
+  </si>
+  <si>
+    <t>RANI PHUL KUMARI K0I0 KA0 SHEERAKOT K0NAM0 1</t>
+  </si>
+  <si>
+    <t>RANI PHUL KUMARI K0I0 KA0 SHEERAKOT K0NAM0 2</t>
+  </si>
+  <si>
+    <t>RANI PHUL KUMARI K0I0 KA0 SHEERAKOT K0NAM0 3</t>
+  </si>
+  <si>
+    <t>RANI PHUL KUMARI K0I0 KA0 SHEERAKOT K0NAM0 4</t>
+  </si>
+  <si>
+    <t>RANI PHUL KUMARI K0I0 KA0 SHEERAKOT K0NAM0 5</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0I0KA0 KALEJ SHERAKOT, KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0I0KA0 KALEJ SHERAKOT, KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0I0KA0 KALEJ SHERAKOT, KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0I0KA0 KALEJ SHERAKOT, KAKSH NAM0 4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 APHAGANAN PRATHAM KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 APHAGANAN PRATHAM, KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 APHAGANAN- DVITIY</t>
+  </si>
+  <si>
+    <t>10 9K|D0 NBDAMSHR SHRCH|DAJ|S|DAI|DAS|DAM |PD|J|D|T|SHR|D</t>
+  </si>
+  <si>
+    <t>DAKSH VAI0I0KA0 SHERAKOT KAKSH NAM. 1</t>
+  </si>
+  <si>
+    <t>DAKSH VAI0I0KA0 SHERAKOT KAKSH NAM. 2</t>
+  </si>
+  <si>
+    <t>DAKSH VAI0I0KA0 SHERAKOT KAKSH NAM. 3</t>
+  </si>
+  <si>
+    <t>DAKSH VAI0I0KA0 SHERAKOT KAKSH NAM. 4</t>
+  </si>
+  <si>
+    <t>DAKSH VAI0I0KA0 SHERAKOT KAKSH NAM. 5</t>
+  </si>
+  <si>
+    <t>DAKSH VAI0I0KA0 SHERAKOT KAKSH NAM. 6</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0ARI0PURV SHERAKOT KAKSH N0 1</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0ARI0PURV SHERAKOT KAKSH N0 2</t>
+  </si>
+  <si>
+    <t>PI0JE0EM0ARI0PURV SHERAKOT KAKSH N0 3</t>
+  </si>
+  <si>
+    <t>JI0P0K0U0MA0VI0 SHERAKOT KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>JI0P0K0U0MA0VI0 SHERAKOT KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM0 4</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM0 5</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM. 6</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM. 8</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0I0KA0 SHERAKOT KAKSH NAM0 7</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL PURANA THANA, SHERAKOT KAKSH-1</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL PURANA THANA, SHERAKOT KAKSH-2</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL PURANA THANA, SHERAKOT KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL PURANA THANA, SHERAKOT KAKSH NAM0 4</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL PURANA THANA, SHERAKOT KAKSH NAM0 5</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0PRA0VI0 SHERAKOT KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0PRA0VI0 SHERAKOT KAKSH NAM. 2</t>
+  </si>
+  <si>
+    <t>AR0YU0EM0PRA0SKUL SHERAKOT KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAMALAPUR UDAYACHAND</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHALIPUR UTTAMACHAMD</t>
+  </si>
+  <si>
+    <t>141CHANATAM DAPAKAKASAM AIBIVAVAS SMJAPACHIMCHANATAM NTACHIM AIPACHAMIPAMSAM TVAVAU.1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 LATIPHAPUR URPH SIPAHIVALA KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BERAKHE.DA TAM.DA KAKSH-01</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BERAKHE.DA TAM.DA KAKSH-02</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 BAJIRAPUR JAGIR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAMAPUR</t>
+  </si>
+  <si>
+    <t>J0I0KA0 MUKARAPURI K0 NAM0-01</t>
+  </si>
+  <si>
+    <t>J0I0KA0 MUKARAPURI K0 NAM0-02</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PALAKI EMAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BALAKISHANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA BUDDHAVA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 UMARAPUR ASHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0MUSTAPHAPUR TAIYAB</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAIDAPUR VIRU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALHAIPUR KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALHAIPUR KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALHAIPUR KAKSH-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALHAIPUR KAKSH-4</t>
+  </si>
+  <si>
+    <t>PAM0GHAR ALHAIPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PAM0GHAR ALHAIPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PAM0GHAR ALHAIPUR KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NURULLAPUR UDAYACHAND KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NURULLAPUR UDAYACHAND KAKSH-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 MAUHADA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIRJAPUR PALLA KAKSH N0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIRJAPUR PALLA KAKSH N0 2</t>
+  </si>
+  <si>
+    <t>KI0SE0KENDR MAU0PUR JAITARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR JAITARA KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR JAITARA KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR JAITARA KAKSH-3</t>
+  </si>
+  <si>
+    <t>KANYA U0MA0VI0 MAU0PUR JAITARA</t>
+  </si>
+  <si>
+    <t>P0I0KA0 MAU0PUR JAITARA KAKSH-01</t>
+  </si>
+  <si>
+    <t>P0I0KA0 MAU0PUR JAITARA KAKSH-02</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAMANAULI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARRA AHAMADAPUR JALAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAJIRAPUR HARAMVASH</t>
+  </si>
+  <si>
+    <t>180 AIBHTBBHDYAK0 K|K|DAIBHT J~NADYABBHDYASHRCHADYASHRCHADY|PDYAK DYACHJBH|CHJDYAJDY|P KL|CHAKDYACHKDYASHRCHADYAK SHRAJDYAJDYACH 1</t>
+  </si>
+  <si>
+    <t>K0PURV MA0VI0 AMAKHEDA KAKSH 2</t>
+  </si>
+  <si>
+    <t>K0PURV0MA0VI0 AMAKHE.DA SHAMJARAPUR KAKSH 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SADULLAKHANAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0VAJIDAPUR VIRU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR VIRU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR BHIAKKAN KAKSH N0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0PUR BHIAKKAN KAKSH N0 2</t>
+  </si>
+  <si>
+    <t>PAMCHAYATAGHAR MAU0PUR SURAJ</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAKATHAL MADHO</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NINDADU KHAS PRATHAM KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NINDADU KHAS PRATHAM KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NINDADU KHAS PRATHAM KAKSH-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NINDADU KHAS DVITIY KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NINDADU KHAS DVITIY KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NINDADU KHAS DVITIY KAKSH-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALAVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHUJISTANAGAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALEMASARAY</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NURULLAPUR CHIMA</t>
+  </si>
+  <si>
+    <t>BA0L0DA0I0KA0 CHAKARAJAMAL KAKSH-1</t>
+  </si>
+  <si>
+    <t>BA0L0DA0I0KA0 CHAKARAJAMAL KAKSH-2</t>
+  </si>
+  <si>
+    <t>RA0K0U0MA0VI0 CHAKARAJAMAL KAKSH-1</t>
+  </si>
+  <si>
+    <t>RA0K0U0MA0VI0 CHAKARAJAMAL KAKSH-2</t>
+  </si>
+  <si>
+    <t>RA0K0U0MA0VI0 CHAKARAJAMAL RA0N0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NASIRAPUR BANAVARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AJITAPUR DASI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAKSHANAPUR KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAKSHANAPUR KAKSH-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MANAPUR SHIAVAPURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAGUPURA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SALARABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 THATHAJAT KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 THATHAJAT KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHEKHAPUR THATH</t>
+  </si>
+  <si>
+    <t>PRA0VI BUAPUR NATTHU KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI BUAPUR NATTHU KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARIYANA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHERAPUR KALIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KESHOPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAJIPUR</t>
+  </si>
+  <si>
+    <t>221CHATAM0 TAPAKALAMSAMLAM SHRAMUMSAMCHANATAM DAMIPACHAMJAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMAPUR DULLI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HASANAPUR PALAKI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAKATHAL SANI KAKSH-01</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAKATHAL SANI KAKSH-02</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MILAKAPURANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA BHAJJA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR NARAYAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JOTAHIMMA KAKSH-01</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JOTAHIMMA KAKSH-02</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UMARAPUR KHADAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAVADA KESHO</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SADDOBER</t>
+  </si>
+  <si>
+    <t>PURV0MA0VI0 RASULAPUR MAU0 KULI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RASULAPUR MAU0 KULI U0K0NAM0-02</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RASULAPUR MAU0 KULI U0K0NAM0-03</t>
+  </si>
+  <si>
+    <t>PU0MA0 VI0 KADARABAD KHURD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AMIRAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JASAMAUR</t>
+  </si>
+  <si>
+    <t>BE0K0PA0KHALILAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SYOHARA KAKSH NAM-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SYOHARA KAKSH NAM-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SYOHARA KAKSH NAM-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SYOHARA KAKSH NAM-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SYOHARA KAKSH NAM-5</t>
+  </si>
+  <si>
+    <t>EM.KYU.I.KA. SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH-1 252EM.KYU.I.KA. SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH-2 253EM.KYU.I.KA. SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH-3 254EM.KYU.I.KA.SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH-4 255EM.KYU.I.KA.SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH-5 256EM.KYU.I.KA.SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH-6 257KI0SE0SAH0SAMI0LI0</t>
+  </si>
+  <si>
+    <t>SYO HARA|VIKAS KARYALAY 258KH0</t>
+  </si>
+  <si>
+    <t>BU259KH0 .DHANAPUR VIKAS SYOHARA KARYA KAKSH-1LAY</t>
+  </si>
+  <si>
+    <t>BU260AR0ES0PI0I0KA0 .DHANAPUR SYOHARA KAKSH-2</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSH NAM0 2 261AR0ES0PI0I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSH NAM0 3 262AR0ES0PI0I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSHARI0NAMKA0 263BIDALA 0 4 SYOHARA</t>
+  </si>
+  <si>
+    <t>KAKSH NAM0 1 RI0KA0 SYOHARA 264BIDALA</t>
+  </si>
+  <si>
+    <t>KAKSH NAM0 2 JAIN MANIDAR SAMITI 265DIGAMBAR</t>
+  </si>
+  <si>
+    <t>I0KA0 SYOHAJAI 266DIGAMBAR ARAN KAKSH-1 MANIDAR SAMITI</t>
+  </si>
+  <si>
+    <t>I0KA0 SYOHAJAI 267DIGAMBAR ARAN KAKSH-2 MANIDAR SAMITI</t>
+  </si>
+  <si>
+    <t>I0KA0 SYOHAJAI 268DIGAMBAR ARAN KAKSH-3 MANIDAR SAMITI</t>
+  </si>
+  <si>
+    <t>I0KA0 SYOHAJAI 269DIGAMBAR ARAN KAKSH-4 MANIDAR SAMITI</t>
+  </si>
+  <si>
+    <t>I0KA0 SYO0HARA 270EM0KYU KAKSH-5 KANYA I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSH0 KANYA 271EM0KYU NAM0 1 I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSH0 KANYA 272EM0KYU NAM0 2 I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSH0 KANYA 273EM0KYU NAM0 3 I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA KAKSH0 KANYA 274EM0KYU NAM0 4 I0KA0</t>
+  </si>
+  <si>
+    <t>SYO HARA NARAYAN 275DHAN KAKSH NAM0RAM 5 NARAYAN</t>
+  </si>
+  <si>
+    <t>276KIMDAM CHAMTAMLAMDAM TMUM CHAMTAMLAMDAM KMDAP DAMIPASAM DAMIM TAPAKALAMSAMLAM AILAVIMTAM TVAVAU CHAVAN 2</t>
+  </si>
+  <si>
+    <t>DANI 277DHANAMAHILA MAHARAMAVI0NARAYAN NARAYAN SYOHARA</t>
+  </si>
+  <si>
+    <t>DANI 278DHANAMAHILA MAHARAMAVI0NARAYAN NARAYAN SYOHARA</t>
+  </si>
+  <si>
+    <t>DANI 279DHANAMAHILA MAHARAMAVI0NARAYAN NARAYAN SYOHARA</t>
+  </si>
+  <si>
+    <t>DANI 280PRAMAHILA MAHA VI0R SYOHARA 0VI0 DINADARAPU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MILAK BENIRAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAMDAURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PALANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHERAPUR RAINI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANAVALI</t>
+  </si>
+  <si>
+    <t>ARDASH JU0HA0 SKUL</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH KAKSH-1 JU0HA0 SKUL</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM NO. 289</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM NO. 290</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM NO. 291</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM NO. 292</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM NO. 293</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM NO. 294</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 295</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 296</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 297</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 298</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 299</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 300</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 301</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 302</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 303</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 304</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 305</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 306</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 307</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 308</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 309</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 310</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 311</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 312</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 313</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 314</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 315</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 316</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 317</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 318</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 319</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 320</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 321</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 322</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 323</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 324</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 325</t>
+  </si>
+  <si>
+    <t>SABDALAPU 288ARDARASH  JU0HA0 SKUL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 326</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1001,8 +1073,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1018,7 +1098,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1026,12 +1106,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1330,70 +1428,127 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="G2" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="H2" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="I2" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="K2" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="L2" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="M2" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="N2" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="O2" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="P2" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="Q2" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="R2" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="S2" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="T2" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -1401,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>1049</v>
@@ -1463,7 +1618,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>629</v>
@@ -1525,7 +1680,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>1176</v>
@@ -1587,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>689</v>
@@ -1649,7 +1804,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>805</v>
@@ -1711,7 +1866,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>810</v>
@@ -1773,7 +1928,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>817</v>
@@ -1835,7 +1990,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>1185</v>
@@ -1897,7 +2052,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>932</v>
@@ -1959,7 +2114,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>1099</v>
@@ -2021,7 +2176,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>709</v>
@@ -2083,7 +2238,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <v>743</v>
@@ -2145,7 +2300,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>713</v>
@@ -2207,7 +2362,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>1000</v>
@@ -2269,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C17">
         <v>1086</v>
@@ -2331,7 +2486,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C18">
         <v>903</v>
@@ -2393,7 +2548,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>1138</v>
@@ -2455,7 +2610,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>1048</v>
@@ -2517,7 +2672,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>720</v>
@@ -2579,7 +2734,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C22">
         <v>774</v>
@@ -2641,7 +2796,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C23">
         <v>722</v>
@@ -2703,7 +2858,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>721</v>
@@ -2765,7 +2920,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>1052</v>
@@ -2827,7 +2982,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>783</v>
@@ -2889,7 +3044,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C27">
         <v>806</v>
@@ -2951,7 +3106,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>734</v>
@@ -3013,7 +3168,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C29">
         <v>1080</v>
@@ -3075,7 +3230,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C30">
         <v>783</v>
@@ -3137,7 +3292,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C31">
         <v>848</v>
@@ -3199,7 +3354,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C32">
         <v>1198</v>
@@ -3261,7 +3416,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>1047</v>
@@ -3323,7 +3478,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C34">
         <v>1229</v>
@@ -3385,7 +3540,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C35">
         <v>746</v>
@@ -3447,7 +3602,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C36">
         <v>773</v>
@@ -3509,7 +3664,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>1023</v>
@@ -3571,7 +3726,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>747</v>
@@ -3633,7 +3788,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C39">
         <v>720</v>
@@ -3695,7 +3850,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C40">
         <v>865</v>
@@ -3757,7 +3912,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>879</v>
@@ -3819,7 +3974,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C42">
         <v>865</v>
@@ -3881,7 +4036,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C43">
         <v>1179</v>
@@ -3943,7 +4098,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C44">
         <v>787</v>
@@ -4005,7 +4160,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C45">
         <v>1023</v>
@@ -4067,7 +4222,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C46">
         <v>663</v>
@@ -4129,7 +4284,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C47">
         <v>735</v>
@@ -4191,7 +4346,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>1018</v>
@@ -4253,7 +4408,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C49">
         <v>954</v>
@@ -4315,7 +4470,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C50">
         <v>678</v>
@@ -4377,7 +4532,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C51">
         <v>671</v>
@@ -4439,7 +4594,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C52">
         <v>633</v>
@@ -4501,7 +4656,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C53">
         <v>646</v>
@@ -4563,7 +4718,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C54">
         <v>1125</v>
@@ -4625,7 +4780,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C55">
         <v>667</v>
@@ -4687,7 +4842,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C56">
         <v>1168</v>
@@ -4749,7 +4904,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C57">
         <v>1166</v>
@@ -4811,7 +4966,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>1123</v>
@@ -4873,7 +5028,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C59">
         <v>675</v>
@@ -4935,7 +5090,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>703</v>
@@ -4997,7 +5152,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C61">
         <v>559</v>
@@ -5059,7 +5214,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C62">
         <v>611</v>
@@ -5121,7 +5276,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C63">
         <v>1235</v>
@@ -5183,7 +5338,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C64">
         <v>769</v>
@@ -5245,7 +5400,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C65">
         <v>1114</v>
@@ -5307,7 +5462,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C66">
         <v>1230</v>
@@ -5369,7 +5524,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C67">
         <v>791</v>
@@ -5431,7 +5586,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C68">
         <v>758</v>
@@ -5493,7 +5648,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C69">
         <v>694</v>
@@ -5555,7 +5710,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C70">
         <v>1237</v>
@@ -5617,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C71">
         <v>820</v>
@@ -5679,7 +5834,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C72">
         <v>815</v>
@@ -5741,7 +5896,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C73">
         <v>1073</v>
@@ -5803,7 +5958,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C74">
         <v>780</v>
@@ -5865,7 +6020,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C75">
         <v>695</v>
@@ -5927,7 +6082,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C76">
         <v>636</v>
@@ -5989,7 +6144,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C77">
         <v>972</v>
@@ -6051,7 +6206,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C78">
         <v>993</v>
@@ -6113,7 +6268,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C79">
         <v>1139</v>
@@ -6175,7 +6330,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C80">
         <v>1126</v>
@@ -6237,7 +6392,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C81">
         <v>986</v>
@@ -6299,7 +6454,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C82">
         <v>986</v>
@@ -6361,7 +6516,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C83">
         <v>825</v>
@@ -6423,7 +6578,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C84">
         <v>1165</v>
@@ -6485,7 +6640,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C85">
         <v>1098</v>
@@ -6547,7 +6702,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C86">
         <v>1225</v>
@@ -6609,7 +6764,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C87">
         <v>1231</v>
@@ -6671,7 +6826,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C88">
         <v>1227</v>
@@ -6733,7 +6888,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C89">
         <v>1063</v>
@@ -6795,7 +6950,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C90">
         <v>961</v>
@@ -6857,7 +7012,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C91">
         <v>930</v>
@@ -6919,7 +7074,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C92">
         <v>793</v>
@@ -6981,7 +7136,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C93">
         <v>627</v>
@@ -7043,7 +7198,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C94">
         <v>643</v>
@@ -7105,7 +7260,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C95">
         <v>690</v>
@@ -7167,7 +7322,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C96">
         <v>668</v>
@@ -7229,7 +7384,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C97">
         <v>838</v>
@@ -7291,7 +7446,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C98">
         <v>963</v>
@@ -7353,7 +7508,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C99">
         <v>935</v>
@@ -7415,7 +7570,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C100">
         <v>928</v>
@@ -7477,7 +7632,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C101">
         <v>1185</v>
@@ -7539,7 +7694,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C102">
         <v>1071</v>
@@ -7601,7 +7756,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C103">
         <v>729</v>
@@ -7663,7 +7818,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C104">
         <v>593</v>
@@ -7725,7 +7880,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C105">
         <v>1245</v>
@@ -7787,7 +7942,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C106">
         <v>881</v>
@@ -7849,7 +8004,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C107">
         <v>918</v>
@@ -7911,7 +8066,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C108">
         <v>972</v>
@@ -7973,7 +8128,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C109">
         <v>687</v>
@@ -8035,7 +8190,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="C110">
         <v>1136</v>
@@ -8097,7 +8252,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C111">
         <v>991</v>
@@ -8159,7 +8314,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C112">
         <v>947</v>
@@ -8221,7 +8376,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C113">
         <v>1217</v>
@@ -8283,7 +8438,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="C114">
         <v>729</v>
@@ -8345,7 +8500,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C115">
         <v>770</v>
@@ -8407,7 +8562,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C116">
         <v>1156</v>
@@ -8469,7 +8624,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C117">
         <v>1189</v>
@@ -8531,7 +8686,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C118">
         <v>1219</v>
@@ -8593,7 +8748,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C119">
         <v>1156</v>
@@ -8655,7 +8810,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C120">
         <v>707</v>
@@ -8717,7 +8872,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C121">
         <v>1034</v>
@@ -8779,7 +8934,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C122">
         <v>1030</v>
@@ -8841,7 +8996,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C123">
         <v>966</v>
@@ -8903,7 +9058,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C124">
         <v>1241</v>
@@ -8965,7 +9120,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C125">
         <v>702</v>
@@ -9027,7 +9182,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C126">
         <v>967</v>
@@ -9089,7 +9244,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="C127">
         <v>1199</v>
@@ -9151,7 +9306,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C128">
         <v>995</v>
@@ -9213,7 +9368,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C129">
         <v>629</v>
@@ -9275,7 +9430,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C130">
         <v>686</v>
@@ -9337,7 +9492,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C131">
         <v>739</v>
@@ -9399,7 +9554,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C132">
         <v>657</v>
@@ -9461,7 +9616,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="C133">
         <v>1147</v>
@@ -9523,7 +9678,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C134">
         <v>901</v>
@@ -9585,7 +9740,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C135">
         <v>1103</v>
@@ -9647,7 +9802,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C136">
         <v>726</v>
@@ -9709,7 +9864,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C137">
         <v>1161</v>
@@ -9771,7 +9926,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C138">
         <v>955</v>
@@ -9833,7 +9988,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C139">
         <v>1119</v>
@@ -9895,7 +10050,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C140">
         <v>957</v>
@@ -9957,7 +10112,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C141">
         <v>924</v>
@@ -10019,7 +10174,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="C142">
         <v>1175</v>
@@ -10081,7 +10236,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C143">
         <v>972</v>
@@ -10143,7 +10298,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C144">
         <v>1096</v>
@@ -10205,7 +10360,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C145">
         <v>798</v>
@@ -10267,7 +10422,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C146">
         <v>1002</v>
@@ -10329,7 +10484,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C147">
         <v>1140</v>
@@ -10391,7 +10546,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C148">
         <v>1216</v>
@@ -10453,7 +10608,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C149">
         <v>896</v>
@@ -10515,7 +10670,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C150">
         <v>767</v>
@@ -10577,7 +10732,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C151">
         <v>1116</v>
@@ -10639,7 +10794,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C152">
         <v>864</v>
@@ -10701,7 +10856,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C153">
         <v>1036</v>
@@ -10763,7 +10918,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C154">
         <v>993</v>
@@ -10825,7 +10980,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C155">
         <v>1152</v>
@@ -10887,7 +11042,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C156">
         <v>1241</v>
@@ -10949,7 +11104,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C157">
         <v>924</v>
@@ -11011,7 +11166,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C158">
         <v>1111</v>
@@ -11073,7 +11228,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C159">
         <v>1133</v>
@@ -11135,7 +11290,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C160">
         <v>999</v>
@@ -11197,7 +11352,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C161">
         <v>1116</v>
@@ -11259,7 +11414,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C162">
         <v>1117</v>
@@ -11321,7 +11476,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C163">
         <v>1110</v>
@@ -11383,7 +11538,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C164">
         <v>1196</v>
@@ -11445,7 +11600,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C165">
         <v>1184</v>
@@ -11507,7 +11662,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C166">
         <v>1037</v>
@@ -11569,7 +11724,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C167">
         <v>666</v>
@@ -11631,7 +11786,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C168">
         <v>644</v>
@@ -11693,7 +11848,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C169">
         <v>817</v>
@@ -11755,7 +11910,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C170">
         <v>758</v>
@@ -11817,7 +11972,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C171">
         <v>1031</v>
@@ -11879,7 +12034,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C172">
         <v>1153</v>
@@ -11941,7 +12096,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C173">
         <v>784</v>
@@ -12003,7 +12158,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C174">
         <v>740</v>
@@ -12065,7 +12220,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C175">
         <v>541</v>
@@ -12127,7 +12282,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C176">
         <v>1043</v>
@@ -12189,7 +12344,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C177">
         <v>1004</v>
@@ -12251,7 +12406,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C178">
         <v>686</v>
@@ -12313,7 +12468,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C179">
         <v>714</v>
@@ -12375,7 +12530,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C180">
         <v>664</v>
@@ -12437,7 +12592,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C181">
         <v>1061</v>
@@ -12499,7 +12654,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C182">
         <v>863</v>
@@ -12561,7 +12716,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C183">
         <v>999</v>
@@ -12623,7 +12778,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C184">
         <v>690</v>
@@ -12685,7 +12840,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C185">
         <v>673</v>
@@ -12747,7 +12902,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="C186">
         <v>1113</v>
@@ -12809,7 +12964,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C187">
         <v>1127</v>
@@ -12871,7 +13026,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C188">
         <v>659</v>
@@ -12933,7 +13088,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="C189">
         <v>1139</v>
@@ -12995,7 +13150,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C190">
         <v>768</v>
@@ -13057,7 +13212,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C191">
         <v>762</v>
@@ -13119,7 +13274,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C192">
         <v>979</v>
@@ -13181,7 +13336,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C193">
         <v>729</v>
@@ -13243,7 +13398,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C194">
         <v>973</v>
@@ -13305,7 +13460,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="C195">
         <v>893</v>
@@ -13367,7 +13522,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="C196">
         <v>605</v>
@@ -13429,7 +13584,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C197">
         <v>691</v>
@@ -13491,7 +13646,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C198">
         <v>1128</v>
@@ -13553,7 +13708,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C199">
         <v>1166</v>
@@ -13615,7 +13770,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C200">
         <v>1117</v>
@@ -13677,7 +13832,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C201">
         <v>963</v>
@@ -13739,7 +13894,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>10</v>
+        <v>212</v>
       </c>
       <c r="C202">
         <v>745</v>
@@ -13801,7 +13956,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C203">
         <v>1049</v>
@@ -13863,7 +14018,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="C204">
         <v>886</v>
@@ -13925,7 +14080,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C205">
         <v>970</v>
@@ -13987,7 +14142,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C206">
         <v>1034</v>
@@ -14049,7 +14204,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C207">
         <v>1107</v>
@@ -14111,7 +14266,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C208">
         <v>641</v>
@@ -14173,7 +14328,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C209">
         <v>749</v>
@@ -14235,7 +14390,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C210">
         <v>642</v>
@@ -14297,7 +14452,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C211">
         <v>623</v>
@@ -14359,7 +14514,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C212">
         <v>668</v>
@@ -14421,7 +14576,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="C213">
         <v>1207</v>
@@ -14483,7 +14638,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C214">
         <v>759</v>
@@ -14545,7 +14700,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C215">
         <v>840</v>
@@ -14607,7 +14762,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="C216">
         <v>834</v>
@@ -14669,7 +14824,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C217">
         <v>975</v>
@@ -14731,7 +14886,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C218">
         <v>1132</v>
@@ -14793,7 +14948,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="C219">
         <v>1098</v>
@@ -14855,7 +15010,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C220">
         <v>1157</v>
@@ -14917,7 +15072,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="C221">
         <v>1104</v>
@@ -14979,7 +15134,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C222">
         <v>978</v>
@@ -15041,7 +15196,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C223">
         <v>839</v>
@@ -15103,7 +15258,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C224">
         <v>1178</v>
@@ -15165,7 +15320,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="C225">
         <v>738</v>
@@ -15227,7 +15382,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C226">
         <v>871</v>
@@ -15289,7 +15444,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="C227">
         <v>893</v>
@@ -15351,7 +15506,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C228">
         <v>593</v>
@@ -15413,7 +15568,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C229">
         <v>727</v>
@@ -15475,7 +15630,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C230">
         <v>1129</v>
@@ -15537,7 +15692,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="C231">
         <v>829</v>
@@ -15599,7 +15754,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C232">
         <v>927</v>
@@ -15661,7 +15816,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C233">
         <v>817</v>
@@ -15723,7 +15878,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C234">
         <v>1135</v>
@@ -15785,7 +15940,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="C235">
         <v>715</v>
@@ -15847,7 +16002,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C236">
         <v>742</v>
@@ -15909,7 +16064,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C237">
         <v>903</v>
@@ -15971,7 +16126,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C238">
         <v>1080</v>
@@ -16033,7 +16188,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C239">
         <v>731</v>
@@ -16095,7 +16250,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C240">
         <v>768</v>
@@ -16157,7 +16312,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C241">
         <v>1193</v>
@@ -16219,7 +16374,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C242">
         <v>483</v>
@@ -16281,7 +16436,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="C243">
         <v>1219</v>
@@ -16343,7 +16498,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C244">
         <v>1019</v>
@@ -16405,7 +16560,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C245">
         <v>787</v>
@@ -16467,7 +16622,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C246">
         <v>680</v>
@@ -16529,7 +16684,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C247">
         <v>978</v>
@@ -16591,7 +16746,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C248">
         <v>958</v>
@@ -16653,7 +16808,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>59</v>
+        <v>254</v>
       </c>
       <c r="C249">
         <v>981</v>
@@ -16715,7 +16870,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C250">
         <v>1196</v>
@@ -16777,7 +16932,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C251">
         <v>528</v>
@@ -16839,7 +16994,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C252">
         <v>1089</v>
@@ -16901,7 +17056,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="C253">
         <v>812</v>
@@ -16963,7 +17118,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C254">
         <v>1123</v>
@@ -17025,7 +17180,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="C255">
         <v>653</v>
@@ -17087,7 +17242,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C256">
         <v>979</v>
@@ -17149,7 +17304,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C257">
         <v>779</v>
@@ -17211,7 +17366,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C258">
         <v>737</v>
@@ -17273,7 +17428,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C259">
         <v>816</v>
@@ -17335,7 +17490,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="C260">
         <v>1183</v>
@@ -17397,7 +17552,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C261">
         <v>1190</v>
@@ -17459,7 +17614,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C262">
         <v>1127</v>
@@ -17521,7 +17676,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
       <c r="C263">
         <v>697</v>
@@ -17583,7 +17738,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C264">
         <v>632</v>
@@ -17645,7 +17800,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C265">
         <v>780</v>
@@ -17707,7 +17862,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C266">
         <v>1171</v>
@@ -17769,7 +17924,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C267">
         <v>1038</v>
@@ -17831,7 +17986,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C268">
         <v>661</v>
@@ -17893,7 +18048,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C269">
         <v>618</v>
@@ -17955,7 +18110,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C270">
         <v>1226</v>
@@ -18017,7 +18172,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C271">
         <v>1079</v>
@@ -18079,7 +18234,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C272">
         <v>1133</v>
@@ -18141,7 +18296,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="C273">
         <v>932</v>
@@ -18203,7 +18358,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>10</v>
+        <v>279</v>
       </c>
       <c r="C274">
         <v>941</v>
@@ -18265,7 +18420,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="C275">
         <v>581</v>
@@ -18327,7 +18482,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C276">
         <v>685</v>
@@ -18389,7 +18544,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C277">
         <v>857</v>
@@ -18451,7 +18606,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C278">
         <v>860</v>
@@ -18513,7 +18668,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C279">
         <v>1225</v>
@@ -18575,7 +18730,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C280">
         <v>1139</v>
@@ -18637,7 +18792,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C281">
         <v>1255</v>
@@ -18699,7 +18854,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C282">
         <v>1056</v>
@@ -18761,7 +18916,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C283">
         <v>1213</v>
@@ -18823,7 +18978,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C284">
         <v>784</v>
@@ -18885,7 +19040,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C285">
         <v>893</v>
@@ -18947,7 +19102,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C286">
         <v>910</v>
@@ -19009,7 +19164,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C287">
         <v>884</v>
@@ -19071,7 +19226,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C288">
         <v>1117</v>
@@ -19133,7 +19288,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C289">
         <v>1054</v>
@@ -19195,7 +19350,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C290">
         <v>874</v>
@@ -19257,7 +19412,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C291">
         <v>1064</v>
@@ -19319,7 +19474,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C292">
         <v>1030</v>
@@ -19381,7 +19536,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C293">
         <v>1065</v>
@@ -19443,7 +19598,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C294">
         <v>1082</v>
@@ -19505,7 +19660,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C295">
         <v>1073</v>
@@ -19567,7 +19722,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="C296">
         <v>967</v>
@@ -19629,7 +19784,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C297">
         <v>824</v>
@@ -19691,7 +19846,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C298">
         <v>854</v>
@@ -19753,7 +19908,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="C299">
         <v>770</v>
@@ -19815,7 +19970,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C300">
         <v>1043</v>
@@ -19877,7 +20032,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C301">
         <v>610</v>
@@ -19939,7 +20094,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C302">
         <v>685</v>
@@ -20001,7 +20156,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C303">
         <v>1105</v>
@@ -20063,7 +20218,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C304">
         <v>1185</v>
@@ -20125,7 +20280,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C305">
         <v>619</v>
@@ -20187,7 +20342,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C306">
         <v>765</v>
@@ -20249,7 +20404,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C307">
         <v>643</v>
@@ -20311,7 +20466,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C308">
         <v>771</v>
@@ -20373,7 +20528,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C309">
         <v>757</v>
@@ -20435,7 +20590,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C310">
         <v>1017</v>
@@ -20497,7 +20652,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C311">
         <v>997</v>
@@ -20559,7 +20714,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C312">
         <v>850</v>
@@ -20621,7 +20776,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C313">
         <v>1118</v>
@@ -20683,7 +20838,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C314">
         <v>1121</v>
@@ -20745,7 +20900,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C315">
         <v>1045</v>
@@ -20807,7 +20962,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C316">
         <v>1033</v>
@@ -20869,7 +21024,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C317">
         <v>1036</v>
@@ -20931,7 +21086,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C318">
         <v>995</v>
@@ -20993,7 +21148,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C319">
         <v>1232</v>
@@ -21055,7 +21210,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>42</v>
+        <v>324</v>
       </c>
       <c r="C320">
         <v>841</v>
@@ -21117,7 +21272,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C321">
         <v>695</v>
@@ -21179,7 +21334,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C322">
         <v>887</v>
@@ -21241,7 +21396,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C323">
         <v>1047</v>
@@ -21303,7 +21458,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>233</v>
+        <v>328</v>
       </c>
       <c r="C324">
         <v>726</v>
@@ -21365,7 +21520,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C325">
         <v>834</v>
@@ -21427,7 +21582,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>10</v>
+        <v>330</v>
       </c>
       <c r="C326">
         <v>1214</v>
@@ -21489,7 +21644,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C327">
         <v>1090</v>
@@ -21551,7 +21706,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C328">
         <v>837</v>
